--- a/Ideas.xlsx
+++ b/Ideas.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Meetu\OutSkill\capstone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{D7F3E6F3-53E1-49A8-97BF-D8B28C7D9D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F977EB-C3DB-4487-AC7B-4B342C310F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{55FDF512-9306-46D2-8166-5930324E0072}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{55FDF512-9306-46D2-8166-5930324E0072}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Requirements" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="167">
   <si>
     <t xml:space="preserve">KYC /AML - Risk model </t>
   </si>
@@ -457,13 +458,808 @@
   </si>
   <si>
     <t>Dual-mode understanding, and persona-driven exploration, Automation code generation (create/modify), what stage the company is? Functional Testing</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Here is a comprehensive </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Software Requirements Specification (SRS) Document</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tailored to your project. It maps the product capabilities directly to the business value and problems outlined in your pitch deck.</t>
+    </r>
+  </si>
+  <si>
+    <t>Software Requirements Specification (SRS)</t>
+  </si>
+  <si>
+    <t>Project: Autonomous QA Tester for Web Apps (AutoQA.AI)</t>
+  </si>
+  <si>
+    <t>1. Introduction &amp; Executive Summary</t>
+  </si>
+  <si>
+    <t>1.1 Purpose</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">This document details the functional and non-functional requirements for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>AutoQA.AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, an autonomous, AI-driven QA testing agent designed to solve the bottlenecks of traditional web application testing.</t>
+    </r>
+  </si>
+  <si>
+    <t>1.2 Business Context &amp; Problem Statement</t>
+  </si>
+  <si>
+    <t>Legacy web application testing suffers from skyrocketing costs and broken production deployments. The core underlying issues are:</t>
+  </si>
+  <si>
+    <r>
+      <t>Manual testing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> is slow, brittle, and structurally incomplete.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Traditional automation scripting</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> requires extensive time to create and maintain.</t>
+    </r>
+  </si>
+  <si>
+    <t>As a company grows, these testing bottlenecks kill revenue and stifle innovation.</t>
+  </si>
+  <si>
+    <t>1.3 Value Proposition &amp; Target Audience</t>
+  </si>
+  <si>
+    <r>
+      <t>Solution:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> An autonomous AI agent that explores web apps like a human user, discovers flaws, and instantly generates its own self-healing, durable regression test suites.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Primary Target Audience:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Next-Gen AI Builders &amp; "Vibe Coders".</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Secondary Target Audience:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Enterprise Agile Software Engineering teams.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Expected Business Impact:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Slashes testing costs by </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>30–40%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, accelerates release velocity, and ensures flawless software effortlessly.</t>
+    </r>
+  </si>
+  <si>
+    <t>2. Scope &amp; Timeline Constraints (7-Week MVP)</t>
+  </si>
+  <si>
+    <t>To achieve rapid deployment within a strict 7-week timeframe, the initial scope is explicitly constrained:</t>
+  </si>
+  <si>
+    <r>
+      <t>Target Application Archetypes:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Scope limited strictly to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SaaS Dashboards</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>E-Commerce Checkout flows</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Automation Framework:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Exclusively outputs and runs on a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Playwright</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> control layer.</t>
+    </r>
+  </si>
+  <si>
+    <t>3. Functional Requirements</t>
+  </si>
+  <si>
+    <t>3.1 Execution &amp; Control Layer (Playwright)</t>
+  </si>
+  <si>
+    <r>
+      <t>FR-1.1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> The system must initialize and orchestrate headless/headed browser sessions using the Playwright framework.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FR-1.2:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> The agent must programmatically execute standard browser actions (clicks, keyboard inputs, hovers, navigation, drag-and-drop).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FR-1.3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> The framework must session-isolate different testing runs to ensure clean states.</t>
+    </r>
+  </si>
+  <si>
+    <t>3.2 Dual-Mode Page Understanding (Vision + DOM)</t>
+  </si>
+  <si>
+    <r>
+      <t>FR-2.1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> For every interactive step, the agent must parse the raw DOM tree to extract element properties, interactive tags (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;button&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;a&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>input</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>), accessibility labels, and IDs.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FR-2.2:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> The agent must simultaneously capture visual screenshots of the viewport.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FR-2.3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> An AI multi-modal engine must fuse DOM structural data with Visual rendering data to accurately locate components, even if elements use dynamic classes or nested shadows (Dual-Mode Understanding).</t>
+    </r>
+  </si>
+  <si>
+    <t>3.3 Persona-Driven Exploration Agent</t>
+  </si>
+  <si>
+    <r>
+      <t>FR-3.1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> The system must support configuration profiles for specific user personas.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FR-3.2:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> The agent must intelligently navigate the app based on the defined active persona:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Admin:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Explores configuration panels, user management, and high-privilege settings.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Paid User:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Focuses on core premium features, dashboard metrics, and creation workflows.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Free User:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Explores basic features, handling upselling walls or restricted limits gracefully.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Anonymous:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Focuses on landing pages, registration/login funnels, and public checkouts.</t>
+    </r>
+  </si>
+  <si>
+    <t>3.4 Bug Detection &amp; Deduction Engine</t>
+  </si>
+  <si>
+    <t>The agent must continuously monitor the application state for anomalies:</t>
+  </si>
+  <si>
+    <r>
+      <t>FR-4.1 (Visual Regressions):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Detect layout shifts, overlapping text, broken images, or unintended UI changes relative to a baseline state.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FR-4.2 (Technical Errors):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Listen to and flag unhandled console errors, syntax exceptions, and failing network requests.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FR-4.3 (Broken Flows):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Identify dead ends, loops, non-responsive buttons, and infinite loading spinners.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FR-4.4 (Network Spikes):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Monitor network traffic and flag a high concentration of HTTP 4xx or 5xx status codes.</t>
+    </r>
+  </si>
+  <si>
+    <t>3.5 Test Code Generation &amp; Output</t>
+  </si>
+  <si>
+    <r>
+      <t>FR-5.1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> As the agent discovers valid user journeys, it must automatically synthesize clean, production-ready </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Playwright automation scripts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FR-5.2:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Generated code must use durable selector strategies (e.g., matching text patterns or roles rather than brittle CSS paths).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FR-5.3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> For every detected bug, the system must automatically file an issue report including:</t>
+    </r>
+  </si>
+  <si>
+    <t>Clear, step-by-step reproducible text steps.</t>
+  </si>
+  <si>
+    <t>A recorded video clip of the test session leading to the failure.</t>
+  </si>
+  <si>
+    <t>Relevant console/network logs.</t>
+  </si>
+  <si>
+    <t>4. Stretch Requirements (Future Iterations)</t>
+  </si>
+  <si>
+    <t>4.1 Continuous CI/CD Mode</t>
+  </si>
+  <si>
+    <r>
+      <t>SR-1.1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Integrate directly into GitHub Actions or GitLab CI/CD pipelines to trigger autonomously upon every code deployment.</t>
+    </r>
+  </si>
+  <si>
+    <t>4.2 Self-Healing Test Suites</t>
+  </si>
+  <si>
+    <r>
+      <t>SR-2.1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> If an existing test fails due to a benign UI change (e.g., a button color change or position shift), the AI engine must automatically rewrite and update the Playwright script to reflect the new state without manual intervention.</t>
+    </r>
+  </si>
+  <si>
+    <t>5. Non-Functional Requirements</t>
+  </si>
+  <si>
+    <t>5.1 Reliability &amp; Durability</t>
+  </si>
+  <si>
+    <r>
+      <t>NFR-1.1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Generated test scripts must achieve a lower flakiness score than traditional manually written scripts, guaranteeing durability.</t>
+    </r>
+  </si>
+  <si>
+    <t>5.2 Performance &amp; Speed</t>
+  </si>
+  <si>
+    <r>
+      <t>NFR-2.1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AI page-understanding inference must be optimized to ensure that the exploration agent does not stall for more than 2-3 seconds per action.</t>
+    </r>
+  </si>
+  <si>
+    <t>5.3 Security &amp; Privacy</t>
+  </si>
+  <si>
+    <r>
+      <t>NFR-3.1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> The agent must securely store and handle sandbox user credentials (Admin, Paid User tokens) without exposing them in generated test logs.</t>
+    </r>
+  </si>
+  <si>
+    <t>Identifying DOM objects</t>
+  </si>
+  <si>
+    <t>Taking screen shots or recording the flows</t>
+  </si>
+  <si>
+    <t>Script creation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">analyse the requirements </t>
+  </si>
+  <si>
+    <t>JIRA/ Confluence</t>
+  </si>
+  <si>
+    <t>Define Personas for the application</t>
+  </si>
+  <si>
+    <t>to do</t>
+  </si>
+  <si>
+    <t>Check if existing playwright agents can read the DOM elements</t>
+  </si>
+  <si>
+    <t>set up the framework so the tools codes accordingly</t>
+  </si>
+  <si>
+    <t>BDD driven framework</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Page object model </t>
+  </si>
+  <si>
+    <t>design pattern we need to follow</t>
+  </si>
+  <si>
+    <t>Check if playwright script be able to access an external website</t>
+  </si>
+  <si>
+    <t>https://www.heroku.com/</t>
+  </si>
+  <si>
+    <t>Mayank</t>
+  </si>
+  <si>
+    <t>Varun</t>
+  </si>
+  <si>
+    <t>Onboard an application</t>
+  </si>
+  <si>
+    <t>Persona based User Journey</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User has to go through the whole journey per persoan, app will caputre the video/screen shots/ </t>
+  </si>
+  <si>
+    <t>These flows have to be captured in the application</t>
+  </si>
+  <si>
+    <t>AutoAI.QA - browser plugin</t>
+  </si>
+  <si>
+    <t>https://www.saucedemo.com/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -527,8 +1323,46 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="14"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -538,6 +1372,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -566,10 +1412,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -587,13 +1434,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -615,14 +1459,55 @@
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -936,7 +1821,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61D6B5F6-9B6A-4AEE-B047-E910221CC9BD}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="42" style="2" customWidth="1"/>
     <col min="3" max="3" width="42.88671875" style="2" customWidth="1"/>
@@ -947,7 +1832,7 @@
     <col min="8" max="8" width="58.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="D1" s="2" t="s">
         <v>15</v>
       </c>
@@ -961,7 +1846,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -972,91 +1857,81 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8">
       <c r="H3" s="2"/>
     </row>
-    <row r="7" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="28.8">
       <c r="B7" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="9"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C7" s="8"/>
+    </row>
+    <row r="8" spans="1:8">
       <c r="B8" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="8"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:8">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="8"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:8">
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="8"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:8">
       <c r="B11" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="8"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:8">
       <c r="B12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="8"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:8">
       <c r="B13" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="8"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:8">
       <c r="B14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="8"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:8">
       <c r="B15" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="8"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:8">
       <c r="B16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="8"/>
-    </row>
-    <row r="17" spans="2:3" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="2:3" ht="28.8">
       <c r="B17" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="8"/>
-    </row>
-    <row r="18" spans="2:3" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="2:3" ht="68.400000000000006" customHeight="1">
       <c r="B18" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3">
       <c r="B19" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3">
       <c r="C20" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="2:3" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" ht="72" customHeight="1">
       <c r="C21" s="2" t="s">
         <v>9</v>
       </c>
@@ -1069,7 +1944,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{296DB166-3310-46A6-9C67-C4B1FC0A5164}">
   <dimension ref="B1:E27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="65.44140625" style="2" customWidth="1"/>
@@ -1077,48 +1952,48 @@
     <col min="5" max="5" width="144.21875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:5">
       <c r="B1" t="s">
         <v>51</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="2:5" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:5" ht="22.8">
       <c r="B2" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5">
       <c r="C3" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B4" s="16" t="s">
+    <row r="4" spans="2:5" ht="22.8">
+      <c r="B4" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" ht="28.8">
       <c r="B5" t="s">
         <v>59</v>
       </c>
@@ -1128,11 +2003,11 @@
       <c r="D5" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="12" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" ht="27.6">
       <c r="B6" t="s">
         <v>61</v>
       </c>
@@ -1142,11 +2017,11 @@
       <c r="D6" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" ht="17.399999999999999">
       <c r="B7" t="s">
         <v>63</v>
       </c>
@@ -1156,27 +2031,27 @@
       <c r="D7" t="s">
         <v>80</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E8" s="12" t="s">
+    <row r="8" spans="2:5">
+      <c r="E8" s="11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="16" t="s">
+    <row r="9" spans="2:5" ht="27.6">
+      <c r="B9" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="11" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" ht="28.8">
       <c r="B10" t="s">
         <v>21</v>
       </c>
@@ -1186,50 +2061,50 @@
       <c r="D10" t="s">
         <v>78</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="2:5" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" ht="22.8">
       <c r="B11" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" ht="17.399999999999999">
       <c r="B12" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="12" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="2:5" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" ht="27.6">
       <c r="B13" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="11" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="E14" s="13" t="s">
+    <row r="14" spans="2:5" ht="17.399999999999999">
+      <c r="E14" s="12" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="16" t="s">
+    <row r="15" spans="2:5">
+      <c r="B15" s="15" t="s">
         <v>65</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -1238,93 +2113,606 @@
       <c r="D15" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="16"/>
-      <c r="E16" s="14"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="16" t="s">
+    <row r="16" spans="2:5">
+      <c r="B16" s="15"/>
+      <c r="E16" s="13"/>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" s="15" t="s">
         <v>67</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5">
       <c r="C18" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5">
       <c r="C19" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="11" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5">
       <c r="C20" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E20" s="14"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E20" s="13"/>
+    </row>
+    <row r="21" spans="2:5">
       <c r="C21" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E22" s="12" t="s">
+    <row r="22" spans="2:5">
+      <c r="E22" s="11" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5">
       <c r="B23" t="s">
         <v>74</v>
       </c>
-      <c r="E23" s="14"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E23" s="13"/>
+    </row>
+    <row r="24" spans="2:5">
       <c r="B24" t="s">
         <v>75</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="14" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" ht="22.8">
       <c r="B25" t="s">
         <v>76</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="2:5" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="E26" s="12" t="s">
+    <row r="26" spans="2:5" ht="27.6">
+      <c r="E26" s="11" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="2:5" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="E27" s="12" t="s">
+    <row r="27" spans="2:5" ht="27.6">
+      <c r="E27" s="11" t="s">
         <v>48</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12817F66-1377-4790-B745-5F9AE1A78926}">
+  <dimension ref="A1:A63"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="206.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="30">
+      <c r="A2" s="18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="22.8">
+      <c r="A3" s="19" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="22.8">
+      <c r="A4" s="19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="17.399999999999999">
+      <c r="A5" s="20" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="17.399999999999999">
+      <c r="A7" s="20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="21" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="22" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="17.399999999999999">
+      <c r="A12" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="21" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="21" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="21" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="21" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="22.8">
+      <c r="A17" s="19" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="21" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="21" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="22.8">
+      <c r="A21" s="19" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="17.399999999999999">
+      <c r="A22" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="24" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="24" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="24" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="17.399999999999999">
+      <c r="A26" s="20" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="24" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="24" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="24" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="17.399999999999999">
+      <c r="A30" s="20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="24" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="24" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="25"/>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="26" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="26" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="26" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="26" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="17.399999999999999">
+      <c r="A38" s="20" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="17" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="21" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="21" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="21" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="21" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="17.399999999999999">
+      <c r="A44" s="20" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="21" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="21" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="22"/>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="23" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="23" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="23" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="22.8">
+      <c r="A52" s="19" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="17.399999999999999">
+      <c r="A53" s="20" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="21" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="17.399999999999999">
+      <c r="A55" s="20" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="21" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="22.8">
+      <c r="A57" s="19" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="17.399999999999999">
+      <c r="A58" s="20" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="21" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="17.399999999999999">
+      <c r="A60" s="20" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="21" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="17.399999999999999">
+      <c r="A62" s="20" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="21" t="s">
+        <v>143</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AD134A7-6C6C-4F9E-8513-4CC0D24A45ED}">
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="91.6640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" customWidth="1"/>
+    <col min="3" max="3" width="3.88671875" customWidth="1"/>
+    <col min="4" max="4" width="85.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="D1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="23.4">
+      <c r="A11" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="18">
+      <c r="A13" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="D13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="17.399999999999999">
+      <c r="A14" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="D14" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="27.6">
+      <c r="A15" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="D15" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="27.6">
+      <c r="A16" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="28" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="17.399999999999999">
+      <c r="A18" s="27" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="27.6">
+      <c r="A19" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="28" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="27.6">
+      <c r="A21" s="28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="17.399999999999999">
+      <c r="A22" s="27" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="28" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="29"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="28" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="28" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="28" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A13" r:id="rId1" xr:uid="{F3E10DB1-4299-41A2-9497-BE56EE2B8557}"/>
+    <hyperlink ref="D19" r:id="rId2" xr:uid="{2280AD5D-8249-4CE3-AEC1-CA17786F2BEC}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>